--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -59,6 +59,9 @@
   </x:si>
   <x:si>
     <x:t>12/07/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/07/23</x:t>
   </x:si>
   <x:si>
     <x:t>QC staus</x:t>
@@ -525,10 +528,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10">
@@ -536,7 +539,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>12</x:v>
@@ -551,70 +554,70 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -46,6 +46,24 @@
     <x:t>Client Tag</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">palestine </x:t>
+  </x:si>
+  <x:si>
+    <x:t>palestine@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/06/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preshan hona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preshan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/06/23</x:t>
+  </x:si>
+  <x:si>
     <x:t>rahlyayaa kang</x:t>
   </x:si>
   <x:si>
@@ -67,9 +85,177 @@
     <x:t>QC staus</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">lomdon </x:t>
+  </x:si>
+  <x:si>
+    <x:t>london@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/06/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/03/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/04/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz2 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6981@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">influence </x:t>
+  </x:si>
+  <x:si>
+    <x:t>influence@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/06/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jason client mia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/09/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 2,tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>eminem emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>america123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 1,tag 2,tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag </x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag10@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz101 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6970@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/07/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mil test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/03/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/05/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabila kang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd123124@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/07/23</x:t>
+  </x:si>
+  <x:si>
     <x:t>raa223441@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">mawaz ijaz </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nawazsharifchor@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">milan </x:t>
+  </x:si>
+  <x:si>
+    <x:t>puraniemailma@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz1 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6982@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz102 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6949@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>move to client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>automation custom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/05/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama3441@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz4 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6987@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/08/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">test </x:t>
+  </x:si>
+  <x:si>
+    <x:t>testnabeel@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/06/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Abcd Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcfh4@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/09/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>clie tim</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/03/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/04/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeelahmed23ee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>add potential client test</x:t>
   </x:si>
   <x:si>
@@ -85,7 +271,70 @@
     <x:t>17/05/23</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
+    <x:t>maryem a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama344@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cutus </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel@outsourcenz.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">branch </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bhola driver </x:t>
+  </x:si>
+  <x:si>
+    <x:t>driverbhola@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz5 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6984@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel 1 ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test0@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/06/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>branch manager</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gr5545 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ninetag@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/07/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
   </x:si>
   <x:si>
     <x:t>potential test</x:t>
@@ -100,13 +349,73 @@
     <x:t>tag 1</x:t>
   </x:si>
   <x:si>
-    <x:t>nabila kang</x:t>
+    <x:t xml:space="preserve">new </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nzimmigrationadvisor@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd34324@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/07/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">imran khan </x:t>
+  </x:si>
+  <x:si>
+    <x:t>imrankhan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test qhem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Word of mouth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag9 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/06/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
   </x:si>
   <x:si>
     <x:t>abcd1234@mail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>11/07/23</x:t>
+    <x:t>nz immi GRANT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz3 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6983@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dubai </x:t>
+  </x:si>
+  <x:si>
+    <x:t>dubaishrjah@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/03/23</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -170,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J6" totalsRowShown="0">
-  <x:autoFilter ref="A1:J6"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J65" totalsRowShown="0">
+  <x:autoFilter ref="A1:J65"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -476,7 +785,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J6"/>
+  <x:dimension ref="A1:J65"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -518,106 +827,1031 @@
       <x:c r="B2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="F4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="G4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="I4" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+    </x:row>
+    <x:row r="7" spans="1:10">
+      <x:c r="A7" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="B7" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
+      <x:c r="F7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:10">
+      <x:c r="A8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:10">
+      <x:c r="A9" s="0" t="s">
         <x:v>16</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:10">
+      <x:c r="A10" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:10">
+      <x:c r="A11" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:10">
+      <x:c r="A12" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
+      <x:c r="A13" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
+      <x:c r="A20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
+      <x:c r="A21" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
+      <x:c r="A22" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
+      <x:c r="A23" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
+      <x:c r="A24" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
+      <x:c r="A25" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
+      <x:c r="A28" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:10">
+      <x:c r="A31" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:10">
+      <x:c r="A32" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:10">
+      <x:c r="A33" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:10">
+      <x:c r="A34" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:10">
+      <x:c r="A35" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10">
+      <x:c r="A36" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10">
+      <x:c r="A37" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10">
+      <x:c r="A38" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10">
+      <x:c r="A39" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
+      <x:c r="A40" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:10">
+      <x:c r="A42" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:10">
+      <x:c r="A43" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:10">
+      <x:c r="A44" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
+      <x:c r="A47" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
+      <x:c r="A51" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J51" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
+      <x:c r="A52" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
+      <x:c r="A53" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:10">
+      <x:c r="A54" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:10">
+      <x:c r="A55" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:10">
+      <x:c r="A56" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:10">
+      <x:c r="A57" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:10">
+      <x:c r="A58" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:10">
+      <x:c r="A59" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:10">
+      <x:c r="A60" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:10">
+      <x:c r="A61" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:10">
+      <x:c r="A62" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:10">
+      <x:c r="A63" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:10">
+      <x:c r="A64" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:10">
+      <x:c r="A65" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>133</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -119,15 +119,6 @@
   </x:si>
   <x:si>
     <x:t>raamamama@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jason client mia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/09/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 2,tag 3 </x:t>
   </x:si>
   <x:si>
     <x:t>eminem emp</x:t>
@@ -479,8 +470,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J65" totalsRowShown="0">
-  <x:autoFilter ref="A1:J65"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J63" totalsRowShown="0">
+  <x:autoFilter ref="A1:J63"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -785,7 +776,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J65"/>
+  <x:dimension ref="A1:J63"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -948,11 +939,14 @@
       <x:c r="A10" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>37</x:v>
@@ -960,47 +954,56 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
@@ -1010,164 +1013,158 @@
       <x:c r="B14" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="J15" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>18</x:v>
@@ -1176,95 +1173,83 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
+      <x:c r="G28" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
         <x:v>75</x:v>
@@ -1272,104 +1257,113 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I33" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J33" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J34" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
@@ -1380,7 +1374,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
         <x:v>12</x:v>
@@ -1388,19 +1382,13 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
@@ -1411,63 +1399,72 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>15</x:v>
@@ -1478,19 +1475,13 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
@@ -1500,256 +1491,262 @@
       <x:c r="B43" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="I50" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J50" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J51" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="I53" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="J56" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>124</x:v>
@@ -1758,55 +1755,52 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H60" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H61" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:10">
@@ -1817,41 +1811,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H63" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:10">
-      <x:c r="A64" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="F64" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G64" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H64" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:10">
-      <x:c r="A65" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G65" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H65" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -127,7 +127,7 @@
     <x:t>america123@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">tag 1,tag 2,tag 3 </x:t>
+    <x:t>tag 1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">tag </x:t>
@@ -325,9 +325,6 @@
     <x:t>05/07/23</x:t>
   </x:si>
   <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
     <x:t>potential test</x:t>
   </x:si>
   <x:si>
@@ -335,9 +332,6 @@
   </x:si>
   <x:si>
     <x:t>25/04/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">new </x:t>
@@ -1497,9 +1491,6 @@
       <x:c r="H43" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="J43" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="0" t="s">
@@ -1514,9 +1505,6 @@
       <x:c r="H44" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="0" t="s">
@@ -1531,84 +1519,81 @@
       <x:c r="H45" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G46" s="0" t="s">
+      <x:c r="H46" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H46" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G47" s="0" t="s">
+      <x:c r="H47" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H47" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G48" s="0" t="s">
+      <x:c r="H48" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H48" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G49" s="0" t="s">
+      <x:c r="H49" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
         <x:v>25</x:v>
@@ -1619,10 +1604,10 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>18</x:v>
@@ -1631,7 +1616,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
         <x:v>66</x:v>
@@ -1642,10 +1627,10 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
         <x:v>12</x:v>
@@ -1656,13 +1641,13 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
         <x:v>81</x:v>
@@ -1673,7 +1658,7 @@
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>101</x:v>
@@ -1682,7 +1667,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="J54" s="0" t="s">
         <x:v>37</x:v>
@@ -1690,7 +1675,7 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
         <x:v>62</x:v>
@@ -1715,7 +1700,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
         <x:v>19</x:v>
@@ -1732,10 +1717,10 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
         <x:v>12</x:v>
@@ -1746,10 +1731,10 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
         <x:v>19</x:v>
@@ -1774,10 +1759,10 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
         <x:v>33</x:v>
@@ -1791,7 +1776,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
         <x:v>19</x:v>
@@ -1805,16 +1790,16 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G63" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="H63" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -217,15 +217,6 @@
     <x:t>17/08/23</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">test </x:t>
-  </x:si>
-  <x:si>
-    <x:t>testnabeel@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07/06/23</x:t>
-  </x:si>
-  <x:si>
     <x:t>Abcd Efgh</x:t>
   </x:si>
   <x:si>
@@ -325,28 +316,10 @@
     <x:t>05/07/23</x:t>
   </x:si>
   <x:si>
-    <x:t>potential test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/04/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/04/23</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">new </x:t>
   </x:si>
   <x:si>
     <x:t>nzimmigrationadvisor@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcd34324@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/07/23</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">imran khan </x:t>
@@ -464,8 +437,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J63" totalsRowShown="0">
-  <x:autoFilter ref="A1:J63"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J57" totalsRowShown="0">
+  <x:autoFilter ref="A1:J57"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -770,7 +743,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J63"/>
+  <x:dimension ref="A1:J57"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -1200,8 +1173,14 @@
       <x:c r="B25" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
         <x:v>69</x:v>
@@ -1211,17 +1190,8 @@
       <x:c r="A26" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="G26" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
         <x:v>72</x:v>
@@ -1229,72 +1199,87 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
+      <x:c r="G31" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
         <x:v>22</x:v>
@@ -1305,205 +1290,193 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F32" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I32" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>89</x:v>
+      <x:c r="F37" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
+      <x:c r="F38" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B39" s="0" t="s">
+      <x:c r="F39" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
@@ -1514,58 +1487,55 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I46" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I47" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
         <x:v>37</x:v>
@@ -1573,56 +1543,44 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I49" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J49" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:10">
@@ -1630,7 +1588,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
         <x:v>12</x:v>
@@ -1641,165 +1599,75 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>115</x:v>
+      <x:c r="F53" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="J54" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G57" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I57" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:10">
-      <x:c r="A58" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G58" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H58" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:10">
-      <x:c r="A59" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F59" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G59" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H59" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:10">
-      <x:c r="A60" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G60" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H60" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:10">
-      <x:c r="A61" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G61" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H61" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:10">
-      <x:c r="A62" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G62" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H62" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:10">
-      <x:c r="A63" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="G63" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H63" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -169,9 +169,6 @@
     <x:t>11/07/23</x:t>
   </x:si>
   <x:si>
-    <x:t>raa223441@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">mawaz ijaz </x:t>
   </x:si>
   <x:si>
@@ -190,24 +187,18 @@
     <x:t>mawaz6982@mail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>mawaz102 test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6949@mail.com</x:t>
+    <x:t>automation custom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/05/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama3441@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>move to client</x:t>
   </x:si>
   <x:si>
-    <x:t>automation custom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/05/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama3441@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>mawaz4 test</x:t>
   </x:si>
   <x:si>
@@ -220,10 +211,7 @@
     <x:t>Abcd Efgh</x:t>
   </x:si>
   <x:si>
-    <x:t>abcfh4@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/09/23</x:t>
+    <x:t>26/02/24</x:t>
   </x:si>
   <x:si>
     <x:t>clie tim</x:t>
@@ -344,6 +332,9 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">jan </x:t>
   </x:si>
   <x:si>
     <x:t>abcd1234@mail.com</x:t>
@@ -437,8 +428,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J57" totalsRowShown="0">
-  <x:autoFilter ref="A1:J57"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J56" totalsRowShown="0">
+  <x:autoFilter ref="A1:J56"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -743,7 +734,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J57"/>
+  <x:dimension ref="A1:J56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -1026,33 +1017,24 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>12</x:v>
@@ -1063,38 +1045,35 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>59</x:v>
@@ -1106,10 +1085,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
         <x:v>60</x:v>
@@ -1119,19 +1098,22 @@
       <x:c r="A22" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>18</x:v>
@@ -1140,163 +1122,154 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="H25" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I31" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>12</x:v>
@@ -1304,44 +1277,44 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10">
@@ -1351,16 +1324,19 @@
       <x:c r="B36" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>88</x:v>
@@ -1369,21 +1345,21 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>15</x:v>
@@ -1394,89 +1370,83 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
+      <x:c r="G40" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
@@ -1486,188 +1456,171 @@
       <x:c r="B45" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I51" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G56" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:10">
-      <x:c r="A57" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G57" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H57" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -211,7 +211,10 @@
     <x:t>Abcd Efgh</x:t>
   </x:si>
   <x:si>
-    <x:t>26/02/24</x:t>
+    <x:t>30/04/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 3 ,tag 2,tag 1</x:t>
   </x:si>
   <x:si>
     <x:t>clie tim</x:t>
@@ -332,9 +335,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">jan </x:t>
   </x:si>
   <x:si>
     <x:t>abcd1234@mail.com</x:t>
@@ -1127,101 +1127,104 @@
       <x:c r="H23" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="I28" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J28" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
         <x:v>22</x:v>
@@ -1232,266 +1235,281 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>79</x:v>
+      <x:c r="F32" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G47" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H47" s="0" t="s">
-        <x:v>74</x:v>
+      <x:c r="J47" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
@@ -1499,10 +1517,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
@@ -1541,7 +1559,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
         <x:v>12</x:v>
@@ -1569,7 +1587,7 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
         <x:v>27</x:v>

--- a/cypress/downloads/Potential_Client_Summary.xlsx
+++ b/cypress/downloads/Potential_Client_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -67,9 +67,6 @@
     <x:t>rahlyayaa kang</x:t>
   </x:si>
   <x:si>
-    <x:t>raa22344erf1@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>facebook</x:t>
   </x:si>
   <x:si>
@@ -79,7 +76,7 @@
     <x:t>12/07/23</x:t>
   </x:si>
   <x:si>
-    <x:t>24/07/23</x:t>
+    <x:t>19/11/24</x:t>
   </x:si>
   <x:si>
     <x:t>QC staus</x:t>
@@ -136,15 +133,6 @@
     <x:t>tag10@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>mawaz101 test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6970@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13/07/23</x:t>
-  </x:si>
-  <x:si>
     <x:t>mil test</x:t>
   </x:si>
   <x:si>
@@ -208,81 +196,84 @@
     <x:t>17/08/23</x:t>
   </x:si>
   <x:si>
+    <x:t>clie tim</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/03/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/04/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeelahmed23ee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>add potential client test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Google or other search</x:t>
+  </x:si>
+  <x:si>
+    <x:t>canada visa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/05/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama344@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cutus </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel@outsourcenz.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jason client mia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/03/25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">branch </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bhola driver </x:t>
+  </x:si>
+  <x:si>
+    <x:t>driverbhola@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz5 test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6984@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel 1 ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test0@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>345</x:t>
+  </x:si>
+  <x:si>
     <x:t>Abcd Efgh</x:t>
   </x:si>
   <x:si>
-    <x:t>30/04/24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 3 ,tag 2,tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>clie tim</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/03/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19/04/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeelahmed23ee123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>add potential client test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Google or other search</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/05/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maryem a</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maryem@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama344@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cutus </x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel@outsourcenz.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">branch </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bhola driver </x:t>
-  </x:si>
-  <x:si>
-    <x:t>driverbhola@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz5 test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6984@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel 1 ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test0@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>345</x:t>
-  </x:si>
-  <x:si>
     <x:t>abcd@mail.com</x:t>
   </x:si>
   <x:si>
@@ -328,6 +319,9 @@
     <x:t>Word of mouth</x:t>
   </x:si>
   <x:si>
+    <x:t>Appeal - IPT</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">tag9 </x:t>
   </x:si>
   <x:si>
@@ -362,6 +356,9 @@
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consultation</x:t>
   </x:si>
   <x:si>
     <x:t>28/03/23</x:t>
@@ -428,8 +425,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J56" totalsRowShown="0">
-  <x:autoFilter ref="A1:J56"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J47" totalsRowShown="0">
+  <x:autoFilter ref="A1:J47"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -734,7 +731,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J56"/>
+  <x:dimension ref="A1:J47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -801,79 +798,76 @@
       <x:c r="A4" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="C4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="F4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
+      <x:c r="I4" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="G5" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="G8" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
@@ -881,194 +875,188 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="G12" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="J12" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1076,569 +1064,416 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I24" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I29" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:10">
-      <x:c r="A48" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G48" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H48" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:10">
-      <x:c r="A49" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G49" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:10">
-      <x:c r="A50" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G50" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H50" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I50" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:10">
-      <x:c r="A51" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G51" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H51" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:10">
-      <x:c r="A52" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G52" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H52" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:10">
-      <x:c r="A53" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G53" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H53" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:10">
-      <x:c r="A54" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G54" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H54" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:10">
-      <x:c r="A55" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F55" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G55" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H55" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:10">
-      <x:c r="A56" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="G56" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H56" s="0" t="s">
-        <x:v>116</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
